--- a/data/trans_dic/IP22D2_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP22D2_R_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 66,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,66</t>
+          <t>0,0; 34,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,78</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,26</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3692</t>
+          <t>0; 2929</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 2958</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2635</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2730</t>
+          <t>0; 2276</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 2073</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3825</t>
+          <t>0; 3710</t>
         </is>
       </c>
     </row>
